--- a/01_clientes/Planilha_Operacional_Cliente_V1.xlsx
+++ b/01_clientes/Planilha_Operacional_Cliente_V1.xlsx
@@ -5,25 +5,26 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Drives compartilhados\V2_GASTROBI\01_clientes\01_restaurante_teste_ativo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Drives compartilhados\V2_GASTROBI\01_clientes\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
     <sheet name="Vendas" sheetId="2" r:id="rId2"/>
     <sheet name="Gastos" sheetId="3" r:id="rId3"/>
     <sheet name="Produtos" sheetId="4" r:id="rId4"/>
-    <sheet name="GERENCIAL_PRIVADO" sheetId="5" r:id="rId5"/>
+    <sheet name="Impostos_monofasicos" sheetId="6" r:id="rId5"/>
+    <sheet name="GERENCIAL_PRIVADO" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="167">
   <si>
     <t>PASSO</t>
   </si>
@@ -497,6 +498,58 @@
   </si>
   <si>
     <t xml:space="preserve">SIM </t>
+  </si>
+  <si>
+    <t>item_produto</t>
+  </si>
+  <si>
+    <t>ncm</t>
+  </si>
+  <si>
+    <t>Cervejas de Malte</t>
+  </si>
+  <si>
+    <t>Refrigerantes</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>Águas Minerais / Gasosas</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>Energéticos e Isotónicos</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Chá pronto para consumo </t>
+  </si>
+  <si>
+    <t>Café Espresso</t>
+  </si>
+  <si>
+    <t>Suco de Laranja Natural</t>
   </si>
 </sst>
 </file>
@@ -506,7 +559,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -541,8 +594,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -553,6 +624,12 @@
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
       </patternFill>
     </fill>
   </fills>
@@ -583,7 +660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -640,6 +717,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3806,6 +3892,84 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="34.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="22">
+        <v>22030000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="22">
+        <v>22021000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="22">
+        <v>22011000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="22">
+        <v>22029900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="22">
+        <v>22021000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="24">
+        <v>9012100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="24">
+        <v>20091900</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
